--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2121,32 +2121,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127414892</v>
+        <v>137454006</v>
       </c>
       <c r="B15" t="n">
-        <v>106244</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>722145</v>
+        <v>722370</v>
       </c>
       <c r="R15" t="n">
-        <v>7215319</v>
+        <v>7215217</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2190,12 +2190,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2226,13 +2236,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127414892</t>
+          <t>https://artportalen.se/Sighting/137454006</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415058</v>
+        <v>127414892</v>
       </c>
       <c r="B16" t="n">
         <v>106244</v>
@@ -2271,13 +2281,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>722217</v>
+        <v>722145</v>
       </c>
       <c r="R16" t="n">
-        <v>7215294</v>
+        <v>7215319</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,13 +2347,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127415058</t>
+          <t>https://artportalen.se/Sighting/127414892</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415060</v>
+        <v>127415058</v>
       </c>
       <c r="B17" t="n">
         <v>106244</v>
@@ -2382,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>722142</v>
+        <v>722217</v>
       </c>
       <c r="R17" t="n">
-        <v>7215315</v>
+        <v>7215294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,16 +2458,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127415060</t>
+          <t>https://artportalen.se/Sighting/127415058</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127414891</v>
+        <v>127415060</v>
       </c>
       <c r="B18" t="n">
-        <v>106229</v>
+        <v>106244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,26 +2475,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2493,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>722199</v>
+        <v>722142</v>
       </c>
       <c r="R18" t="n">
-        <v>7215267</v>
+        <v>7215315</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,13 +2569,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127414891</t>
+          <t>https://artportalen.se/Sighting/127415060</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127415059</v>
+        <v>127414891</v>
       </c>
       <c r="B19" t="n">
         <v>106229</v>
@@ -2595,7 +2605,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2604,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>722192</v>
+        <v>722199</v>
       </c>
       <c r="R19" t="n">
-        <v>7215271</v>
+        <v>7215267</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2669,6 +2679,117 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414891</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127415059</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>722192</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7215271</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127415059</t>
         </is>
@@ -2694,6 +2815,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -2124,7 +2124,7 @@
         <v>137454006</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
